--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487918_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487918_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5489</v>
+        <v>8.452199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0876</v>
+        <v>6.9322</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4613</v>
+        <v>1.52</v>
       </c>
       <c r="G2" t="n">
         <v>4.9998</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5085</v>
+        <v>1.4118</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1646</v>
+        <v>1.0092</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3439</v>
+        <v>0.4026</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6378</v>
+        <v>3.4856</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2406</v>
+        <v>1.5445</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8785</v>
+        <v>1.9411</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3871</v>
+        <v>2.3705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8572</v>
+        <v>-1.2348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5299</v>
+        <v>3.6053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4279</v>
+        <v>2.8851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4369</v>
+        <v>-0.0752</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.008999999999999999</v>
+        <v>2.9603</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9592000000000001</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4203</v>
+        <v>-1.1596</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5389</v>
+        <v>0.645</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>2.4974</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3507</v>
+        <v>-0.3417</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8663</v>
+        <v>-0.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4843</v>
+        <v>-0.0417</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5258</v>
+        <v>2.8722</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8783</v>
+        <v>-1.3897</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6475</v>
+        <v>4.2619</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3705</v>
+        <v>1.3871</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2348</v>
+        <v>0.8572</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6053</v>
+        <v>0.5299</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8851</v>
+        <v>0.4279</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0752</v>
+        <v>0.4369</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9603</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1596</v>
+        <v>0.4203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.645</v>
+        <v>0.5389</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4568</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4974</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3016</v>
+        <v>1.585</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9663</v>
+        <v>0.7173</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3353</v>
+        <v>0.8678</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4259</v>
+        <v>1.8211</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1161</v>
+        <v>1.6875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3097</v>
+        <v>0.1336</v>
       </c>
       <c r="G5" t="n">
         <v>2.3003</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2088</v>
+        <v>-0.396</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>-0.3667</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1468</v>
+        <v>-0.0293</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7076</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2658</v>
+        <v>1.642</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7264</v>
+        <v>-0.804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5394</v>
+        <v>2.446</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1016</v>
+        <v>4.3095</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3113</v>
+        <v>1.0299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7903</v>
+        <v>3.2796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.975</v>
+        <v>3.1055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9358</v>
+        <v>1.1853</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>1.9202</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1266</v>
+        <v>1.204</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3755</v>
+        <v>-0.1553</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7511</v>
+        <v>1.3594</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0626</v>
+        <v>-0.9807</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2486</v>
+        <v>-0.7877</v>
       </c>
       <c r="U6" t="n">
-        <v>0.186</v>
+        <v>-0.193</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9911</v>
+        <v>1.4699</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1907</v>
+        <v>1.0479</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1817</v>
+        <v>0.422</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3095</v>
+        <v>2.1016</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0299</v>
+        <v>1.3113</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2796</v>
+        <v>0.7903</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1055</v>
+        <v>0.975</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1853</v>
+        <v>0.9358</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9202</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>1.204</v>
+        <v>1.1266</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1553</v>
+        <v>0.3755</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3594</v>
+        <v>0.7511</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6317</v>
+        <v>0.1414</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1744</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4573</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9206</v>
+        <v>1.4079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2953</v>
+        <v>0.7239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6253</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>3.0209</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5571</v>
+        <v>-0.0698</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5748</v>
+        <v>-0.1462</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0177</v>
+        <v>0.0764</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7513</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7406</v>
+        <v>0.913</v>
       </c>
       <c r="E9" t="n">
-        <v>0.302</v>
+        <v>0.4744</v>
       </c>
       <c r="F9" t="n">
         <v>0.4385</v>
@@ -1156,10 +1156,10 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7144</v>
+        <v>-0.542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6524</v>
+        <v>-0.48</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0619</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4437</v>
+        <v>0.4326</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.5171</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4368</v>
+        <v>-0.0844</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3411</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9336</v>
+        <v>0.9225</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1273</v>
+        <v>0.7639</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1937</v>
+        <v>0.1586</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8137</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2674</v>
+        <v>-0.9173</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0866</v>
+        <v>-3.1842</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1807</v>
+        <v>2.2669</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0788</v>
+        <v>-0.3718</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0788</v>
+        <v>-0.642</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.2702</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0192</v>
+        <v>-0.7145</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0192</v>
+        <v>0.2318</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.9463</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.098</v>
+        <v>0.3426</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.098</v>
+        <v>-0.8738</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.2165</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6244</v>
+        <v>2.7055</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1885</v>
+        <v>-0.0023</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.3886</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1233</v>
+        <v>0.3863</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5439</v>
+        <v>-1.238</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9576</v>
+        <v>-1.0866</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4137</v>
+        <v>-0.1514</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3718</v>
+        <v>-0.0788</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.642</v>
+        <v>-0.0788</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2702</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7145</v>
+        <v>0.0192</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2318</v>
+        <v>0.0192</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9463</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3426</v>
+        <v>-0.098</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8738</v>
+        <v>-0.098</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2165</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.6244</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-2.0812</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.7055</v>
-      </c>
       <c r="S12" t="n">
-        <v>-0.6289</v>
+        <v>-0.1592</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.162</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5331</v>
+        <v>-0.0939</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6889</v>
+        <v>20.3412</v>
       </c>
       <c r="E13" t="n">
-        <v>5.810699999999999</v>
+        <v>6.462999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>13.8781</v>
+        <v>13.8782</v>
       </c>
       <c r="G13" t="n">
         <v>19.8397</v>
@@ -1444,7 +1444,7 @@
         <v>12.4935</v>
       </c>
       <c r="K13" t="n">
-        <v>7.533900000000001</v>
+        <v>7.533899999999999</v>
       </c>
       <c r="L13" t="n">
         <v>4.9596</v>
@@ -1468,13 +1468,13 @@
         <v>16.6494</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9167999999999996</v>
+        <v>1.569</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6235999999999998</v>
+        <v>0.02890000000000013</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5403</v>
+        <v>1.5404</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1487</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1025</v>
+        <v>4.1815</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7286</v>
+        <v>3.3712</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3739</v>
+        <v>0.8103</v>
       </c>
       <c r="G14" t="n">
         <v>2.4063</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4662</v>
+        <v>1.5452</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3852</v>
+        <v>1.0278</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0809</v>
+        <v>0.5174</v>
       </c>
       <c r="V14" t="n">
         <v>0.23</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7983</v>
+        <v>2.1745</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7774</v>
+        <v>4.0989</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9792</v>
+        <v>-1.9244</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4766</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8383</v>
+        <v>-0.4621</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8234</v>
+        <v>-0.5019</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.015</v>
+        <v>0.0398</v>
       </c>
       <c r="V15" t="n">
         <v>2.4483</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4858</v>
+        <v>-0.5778</v>
       </c>
       <c r="E16" t="n">
         <v>-2.5248</v>
       </c>
       <c r="F16" t="n">
-        <v>2.039</v>
+        <v>1.947</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9471</v>
@@ -1702,13 +1702,13 @@
         <v>2.9137</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.5839</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1123</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7882</v>
+        <v>0.6962</v>
       </c>
       <c r="V16" t="n">
         <v>4.3234</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GUEYE</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7643</v>
+        <v>-0.6169</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1957</v>
+        <v>1.5255</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5686</v>
+        <v>-2.1424</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3879</v>
+        <v>-3.0625</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5308</v>
+        <v>-1.3774</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1429</v>
+        <v>-1.6851</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.6415</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.7625</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3879</v>
+        <v>-2.421</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5308</v>
+        <v>-1.4985</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1429</v>
+        <v>-0.9225</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3764</v>
+        <v>-0.1569</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>0.0401</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1807</v>
+        <v>-0.197</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>D. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7726</v>
+        <v>-0.7389</v>
       </c>
       <c r="E18" t="n">
-        <v>0.454</v>
+        <v>-0.1957</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2266</v>
+        <v>-0.5432</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0625</v>
+        <v>-0.3879</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3774</v>
+        <v>-0.5308</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6851</v>
+        <v>0.1429</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6415</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7625</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.421</v>
+        <v>-0.3879</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4985</v>
+        <v>-0.5308</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9225</v>
+        <v>0.1429</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3126</v>
+        <v>-0.351</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0315</v>
+        <v>-0.1957</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2811</v>
+        <v>-0.1553</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2577</v>
+        <v>-2.0268</v>
       </c>
       <c r="E19" t="n">
         <v>-2.0428</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2149</v>
+        <v>0.016</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7292</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4652</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3699</v>
+        <v>-0.139</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3849</v>
+        <v>-2.1055</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9556</v>
+        <v>-1.8484</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4293</v>
+        <v>-0.2571</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7286</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7477</v>
+        <v>-0.4683</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7705</v>
+        <v>-0.6634</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0229</v>
+        <v>0.1951</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1168</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4861</v>
+        <v>-4.3227</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.6137</v>
+        <v>-6.828</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1276</v>
+        <v>2.5054</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7801</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2838</v>
+        <v>0.4472</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1247</v>
+        <v>-0.339</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4085</v>
+        <v>0.7862</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1168</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7969</v>
+        <v>-6.3707</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4337</v>
+        <v>-4.3265</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3632</v>
+        <v>-2.0441</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6513</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0289</v>
+        <v>-0.6027</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5748</v>
+        <v>-0.4676</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4541</v>
+        <v>-0.135</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2843</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.6412</v>
+        <v>-7.8569</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0719</v>
+        <v>-5.1075</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5694</v>
+        <v>-2.7494</v>
       </c>
       <c r="G23" t="n">
         <v>-6.483</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3425</v>
+        <v>0.4418</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9663</v>
+        <v>-0.0019</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6238</v>
+        <v>0.4437</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2726</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.6887</v>
+        <v>-18.2602</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.8782</v>
+        <v>-13.8781</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.8107</v>
+        <v>-4.3819</v>
       </c>
       <c r="G24" t="n">
         <v>-19.84</v>
@@ -2314,7 +2314,7 @@
         <v>-7.534</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.959600000000001</v>
+        <v>-4.9596</v>
       </c>
       <c r="P24" t="n">
         <v>-2.081399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>14.5683</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9165999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5402</v>
+        <v>-1.5401</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6234999999999999</v>
+        <v>2.0521</v>
       </c>
       <c r="V24" t="n">
         <v>3.1488</v>
